--- a/tools/excel_export/excel/mall_items.xlsx
+++ b/tools/excel_export/excel/mall_items.xlsx
@@ -94,10 +94,10 @@
     <t>每日补给</t>
   </si>
   <si>
-    <t>金币 200 + 通用英雄经验 100</t>
-  </si>
-  <si>
-    <t>[{"type":"gold","amount":200},{"type":"hero_exp","amount":100}]</t>
+    <t>金币 100 + 通用英雄经验 100</t>
+  </si>
+  <si>
+    <t>[{"type":"gold","amount":100},{"type":"hero_exp","amount":100}]</t>
   </si>
   <si>
     <t>gold</t>
@@ -109,10 +109,10 @@
     <t>金币袋</t>
   </si>
   <si>
-    <t>+300 金币</t>
-  </si>
-  <si>
-    <t>[{"type":"gold","amount":300}]</t>
+    <t>+200 金币</t>
+  </si>
+  <si>
+    <t>[{"type":"gold","amount":200}]</t>
   </si>
   <si>
     <t>shop_gold</t>
